--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C15"/>
+  <dimension ref="B1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="2" max="2"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>・RT 発言順（荒木田 9/29 決定）: メンバー国アルファベット順（Japan の直後に仙台市）→ 希望があればアドバイザー国（AUS/NZ）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン UNDP/WMO）。Part 1 は Armenia〜Turkiye（22枠×5分＝13:03〜14:53）、Part 2 は Uzbekistan・Viet Nam＋機関。登録国で当日までに確定し、未登録国の行は削除する。</t>
+          <t>・RT 発言順（荒木田 9/29 決定）: メンバー国アルファベット順（Japan の直後に仙台市）→ 希望があればアドバイザー国（AUS/NZ）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン UNDP/WMO）。Part 1 は Armenia〜Turkiye（Azerbaijan 辞退で 21枠×5分＝13:03〜14:48、予備 14:48〜14:55）、Part 2 は Uzbekistan・Viet Nam＋機関。登録国で当日までに確定し、未登録国の行は削除する。</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P42"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>アルメニアとアゼルバイジャンは配席上離してあるが、発言順はアルファベット順で連続（荒木田 9/29 決定）。</t>
+          <t>アルメニアとアゼルバイジャンは配席上離してあるが、発言順はアルファベット順で連続（荒木田 9/29 決定）。 Azerbaijan は RT で発言しない（10/1 Rustamzade 氏→吉田）ため行を削除。10/2 時点の RT 登録: Armenia, Bhutan, Cambodia, Japan, Maldives, ROK, Singapore(SCDF), Sri Lanka, Thailand, Turkiye, Viet Nam＋仙台市、NZ、ADPC、Google（吉田名簿 1002）。未登録のメンバー国は行を残し、当日までに確定。</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Azerbaijan</t>
+          <t>Statement: the delegation of Bangladesh</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-2: Azerbaijan</t>
+          <t>PPT 09-2: Bangladesh</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Azerbaijan. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Bangladesh. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Bangladesh</t>
+          <t>Statement: the delegation of Bhutan</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-3: Bangladesh</t>
+          <t>PPT 09-3: Bhutan</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Bangladesh. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Bhutan. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1669,17 +1669,17 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Bhutan</t>
+          <t>Statement: the delegation of Brunei Darussalam</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-4: Bhutan</t>
+          <t>PPT 09-4: Brunei Darussalam</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Bhutan. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Brunei Darussalam. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Brunei Darussalam</t>
+          <t>Statement: the delegation of Cambodia</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-5: Brunei Darussalam</t>
+          <t>PPT 09-5: Cambodia</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Brunei Darussalam. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Cambodia. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1819,17 +1819,17 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Cambodia</t>
+          <t>Statement: the delegation of Fiji</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-6: Cambodia</t>
+          <t>PPT 09-6: Fiji</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Cambodia. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Fiji. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1894,17 +1894,17 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Fiji</t>
+          <t>Statement: the delegation of India</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-7: Fiji</t>
+          <t>PPT 09-7: India</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Fiji. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of India. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -1969,24 +1969,24 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of India</t>
+          <t>Statement: the delegation of Japan</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-8: India</t>
+          <t>PPT 09-8: Japan</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of India. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Japan, Cabinet Office. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
+          <t>日本のステートメントは中根補佐（Mr NAKANE Toru, Director, International Relations Division, Disaster Management Bureau, Cabinet Office）。荒木田 10/1 確定、内閣府スケジュール 9/28 版と一致。林副大臣は Opening 後に退席、御手洗参事官は SIDEX 視察・MHA 同行で RT Part 1 不在。</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2044,24 +2044,24 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Japan</t>
+          <t>Statement: Mr TAKAHASHI Shinichi</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-9: Japan</t>
+          <t>PPT 09-9: City of Sendai</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Japan, Cabinet Office. You have 5 minutes, please.
+          <t>Next, I would like to invite Mr TAKAHASHI Shinichi, Vice Mayor of the City of Sendai, Japan. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>日本のステートメントは中根補佐（Mr NAKANE Toru, Director, International Relations Division, Disaster Management Bureau, Cabinet Office）。荒木田 10/1 確定、内閣府スケジュール 9/28 版と一致。林副大臣は Opening 後に退席、御手洗参事官は SIDEX 視察・MHA 同行で RT Part 1 不在。</t>
+          <t>日本の直後に仙台市（教室列1列目の卓上マイク）。次期 APMCDRR・ACDR2027 ホスト市としての紹介を含む見込み。</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2119,24 +2119,24 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Statement: Mr TAKAHASHI Shinichi</t>
+          <t>Statement: the delegation of Lao PDR</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-10: City of Sendai</t>
+          <t>PPT 09-10: Lao PDR</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite Mr TAKAHASHI Shinichi, Vice Mayor of the City of Sendai, Japan. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Lao PDR. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>日本の直後に仙台市（教室列1列目の卓上マイク）。次期 APMCDRR・ACDR2027 ホスト市としての紹介を含む見込み。</t>
+          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -2194,17 +2194,17 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Lao PDR</t>
+          <t>Statement: the delegation of Malaysia</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-11: Lao PDR</t>
+          <t>PPT 09-11: Malaysia</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Lao PDR. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Malaysia. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Malaysia</t>
+          <t>Statement: the delegation of Maldives</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-12: Malaysia</t>
+          <t>PPT 09-12: Maldives</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Malaysia. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Maldives. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2344,17 +2344,17 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Maldives</t>
+          <t>Statement: the delegation of Mongolia</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-13: Maldives</t>
+          <t>PPT 09-13: Mongolia</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Maldives. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Mongolia. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2419,17 +2419,17 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Mongolia</t>
+          <t>Statement: the delegation of Myanmar</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-14: Mongolia</t>
+          <t>PPT 09-14: Myanmar</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Mongolia. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Myanmar. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2494,17 +2494,17 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Myanmar</t>
+          <t>Statement: the delegation of Pakistan</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-15: Myanmar</t>
+          <t>PPT 09-15: Pakistan</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Myanmar. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Pakistan. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2569,17 +2569,17 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Pakistan</t>
+          <t>Statement: the delegation of Papua New Guinea</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-16: Pakistan</t>
+          <t>PPT 09-16: Papua New Guinea</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Pakistan. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Papua New Guinea. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Papua New Guinea</t>
+          <t>Statement: the delegation of Republic of Korea</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-17: Papua New Guinea</t>
+          <t>PPT 09-17: Republic of Korea</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Papua New Guinea. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Republic of Korea. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2719,24 +2719,24 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Republic of Korea</t>
+          <t>Statement: the delegation of Singapore</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-18: Republic of Korea</t>
+          <t>PPT 09-18: Singapore</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Republic of Korea. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Singapore. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
+          <t>アルファベット順どおり Singapore の位置。Commissioner か Alan Chow 氏か【TBC】。</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Singapore</t>
+          <t>Statement: the delegation of Sri Lanka</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-19: Singapore</t>
+          <t>PPT 09-19: Sri Lanka</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Singapore. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Sri Lanka. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>アルファベット順どおり Singapore の位置。Commissioner か Alan Chow 氏か【TBC】。</t>
+          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Sri Lanka</t>
+          <t>Statement: the delegation of Thailand</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-20: Sri Lanka</t>
+          <t>PPT 09-20: Thailand</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Sri Lanka. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Thailand. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2944,17 +2944,17 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Thailand</t>
+          <t>Statement: the delegation of Turkiye</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-21: Thailand</t>
+          <t>PPT 09-21: Turkiye</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Thailand. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Turkiye. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -3019,51 +3019,45 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Turkiye</t>
+          <t>予備時間・Part 1 締め</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-22: Turkiye</t>
+          <t>PPT 11: Comments &amp; Questions（提出方法）</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Turkiye. You have 5 minutes, please.
-（ステートメント 5分）
-Thank you very much.</t>
+          <t>We have a few minutes before the end of Part 1. If any delegation wishes to add a brief comment on what we have heard, please raise your name plate. [If none:] Please also use the comment sheets on your desk; they will be collected by the secretariat during the coffee break.</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
+          <t>進行が押した場合はこの枠を吸収に使う。Azerbaijan の発言辞退（10/1）で 1 枠（5 分）空いた分もここに入る（14:48-14:55）。</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>着席発言（卓上マイク）</t>
+          <t>Moderator</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>紹介・御礼</t>
+          <t>進行</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>国名スライド</t>
+          <t>PPT 11</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>卓上マイク ON 確認</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: 発言者</t>
-        </is>
-      </c>
+          <t>スタンド/ハンドマイク</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="inlineStr">
         <is>
           <t>記録</t>
@@ -3074,174 +3068,105 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
-        <is>
-          <t>発言者写真</t>
-        </is>
-      </c>
-      <c r="P39" s="7" t="inlineStr">
-        <is>
-          <t>Q&amp;A欄監視</t>
-        </is>
-      </c>
+      <c r="O39" s="7" t="n"/>
+      <c r="P39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>予備時間・Part 1 締め</t>
+          <t>RT Part 1 まとめ・連絡事項</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>PPT 11: Comments &amp; Questions（提出方法）</t>
+          <t>PPT 12: Info（Coffee / SC / Gala）</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>We have a few minutes before the end of Part 1. If any delegation wishes to add a brief comment on what we have heard, please raise your name plate. [If none:] Please also use the comment sheets on your desk; they will be collected by the secretariat during the coffee break.</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>進行が押した場合はこの枠を吸収に使う。</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Moderator</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>進行</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>PPT 11</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>スタンド/ハンドマイク</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>記録</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>記録</t>
-        </is>
-      </c>
-      <c r="O40" s="7" t="n"/>
-      <c r="P40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>RT Part 1 まとめ・連絡事項</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>PPT 12: Info（Coffee / SC / Gala）</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Thank you for your statements. This concludes Part 1 of the Roundtable. The remaining statements will be delivered tomorrow morning in Part 2, starting at 9 o’clock sharp in this room.
 Three announcements. First, coffee is served in front of this room. Second, the Steering Committee Meeting for ADRC member countries only will start at 15:15 in this room. Delegates of member countries, please return by 15:15. Third, for participants attending the SIDEX Gala Dinner, the bus will leave from Dorsett Changi City Hotel at 17:30. Thank you.</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>SC の前方席: 議長＝内閣府 中根補佐（内閣府スケジュール 9/28 版で「SC モデレーター」）、ADRC 宮木所長。SC 開始までに机上の RT 資料を回収（吉田・塩見）。</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>Moderator</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>読み上げ</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>PPT 12</t>
         </is>
       </c>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Webinar 一時停止（SC は別 Zoom）</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>記録終了</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>記録終了</t>
         </is>
       </c>
-      <c r="O41" s="7" t="n"/>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="O40" s="7" t="n"/>
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>録画停止・保存</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="6" t="n">
+    <row r="41">
+      <c r="B41" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>15:00-15:15</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Coffee Break</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>コーヒー: Peridot 前。SC 用に前方席の名札を差し替え（吉田・田中）。Gerry は RT ノートを整理し Summary 執筆へ。</t>
         </is>
       </c>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="6" t="n"/>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="B1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>原稿: ACDR2026_Opening_Remarks_MIURA_draft1002_clean.docx（児玉 rev4 を受入、英語551語＝約4分、ヘッダー 12:56-13:00）。10/2 に三浦センター長へ送付、確認待ち。Sylvia 9/30: Commissioner 5分、Chairman は短めの要望。3分に詰める場合は後半の段落を削る。</t>
+          <t>原稿: ACDR2026_Opening_Remarks_MIURA_draft1002_clean.docx（児玉 rev4 を受入、英語551語＝約4分、ヘッダー 12:56-13:00）。10/2 に三浦センター長へ送付、10/5 16:22 返信「これでよろしい。当日多少アドリブを入れるかもしれないが基本はこれで」→ 確定版。Sylvia 9/30: Commissioner 5分、Chairman は短めの要望。3分に詰める場合は後半の段落を削る。</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1004.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>・RT 発言順（荒木田 9/29 決定）: メンバー国アルファベット順（Japan の直後に仙台市）→ 希望があればアドバイザー国（AUS/NZ）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン UNDP/WMO）。Part 1 は Armenia〜Turkiye（Azerbaijan 辞退で 21枠×5分＝13:03〜14:48、予備 14:48〜14:55）、Part 2 は Uzbekistan・Viet Nam＋機関。登録国で当日までに確定し、未登録国の行は削除する。</t>
+          <t>・RT 発言順（荒木田 9/29 決定）: メンバー国アルファベット順（Japan の直後に仙台市）→ 希望があればアドバイザー国（AUS/NZ）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン UNDP/WMO）。Part 1 は Armenia〜Turkiye（Azerbaijan・Lao PDR 辞退で 20枠×5分＝13:03〜14:43、予備 14:43〜14:55）、Part 2 は Uzbekistan・Viet Nam＋機関。登録国で当日までに確定し、未登録国の行は削除する。</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P41"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>アルメニアとアゼルバイジャンは配席上離してあるが、発言順はアルファベット順で連続（荒木田 9/29 決定）。 Azerbaijan は RT で発言しない（10/1 Rustamzade 氏→吉田）ため行を削除。10/2 時点の RT 登録: Armenia, Bhutan, Cambodia, Japan, Maldives, ROK, Singapore(SCDF), Sri Lanka, Thailand, Turkiye, Viet Nam＋仙台市、NZ、ADPC、Google（吉田名簿 1002）。未登録のメンバー国は行を残し、当日までに確定。</t>
+          <t>アルメニアとアゼルバイジャンは配席上離してあるが、発言順はアルファベット順で連続（荒木田 9/29 決定）。 Azerbaijan は RT で発言しない（10/1 Rustamzade 氏→吉田）ため行を削除。10/2 時点の RT 登録: Armenia, Bhutan, Cambodia, Japan, Maldives, ROK, Singapore(SCDF), Sri Lanka, Thailand, Turkiye, Viet Nam＋仙台市、NZ、ADPC、Google（吉田名簿 1002）。未登録のメンバー国は行を残し、当日までに確定。 10/5 吉田: Pakistan が RT 登録、Lao PDR は発言しない（出席はする）→ Lao PDR の行を削除。</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Lao PDR</t>
+          <t>Statement: the delegation of Malaysia</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-10: Lao PDR</t>
+          <t>PPT 09-10: Malaysia</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Lao PDR. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Malaysia. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2194,17 +2194,17 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Malaysia</t>
+          <t>Statement: the delegation of Maldives</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-11: Malaysia</t>
+          <t>PPT 09-11: Maldives</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Malaysia. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Maldives. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Maldives</t>
+          <t>Statement: the delegation of Mongolia</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-12: Maldives</t>
+          <t>PPT 09-12: Mongolia</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Maldives. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Mongolia. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2344,17 +2344,17 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Mongolia</t>
+          <t>Statement: the delegation of Myanmar</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-13: Mongolia</t>
+          <t>PPT 09-13: Myanmar</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Mongolia. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Myanmar. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2419,17 +2419,17 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Myanmar</t>
+          <t>Statement: the delegation of Pakistan</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-14: Myanmar</t>
+          <t>PPT 09-14: Pakistan</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Myanmar. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Pakistan. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2494,17 +2494,17 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Pakistan</t>
+          <t>Statement: the delegation of Papua New Guinea</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-15: Pakistan</t>
+          <t>PPT 09-15: Papua New Guinea</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Pakistan. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Papua New Guinea. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2569,17 +2569,17 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Papua New Guinea</t>
+          <t>Statement: the delegation of Republic of Korea</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-16: Papua New Guinea</t>
+          <t>PPT 09-16: Republic of Korea</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Papua New Guinea. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Republic of Korea. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2644,24 +2644,24 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Republic of Korea</t>
+          <t>Statement: the delegation of Singapore</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-17: Republic of Korea</t>
+          <t>PPT 09-17: Singapore</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Republic of Korea. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Singapore. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
+          <t>アルファベット順どおり Singapore の位置。Commissioner か Alan Chow 氏か【TBC】。</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -2719,24 +2719,24 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Singapore</t>
+          <t>Statement: the delegation of Sri Lanka</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-18: Singapore</t>
+          <t>PPT 09-18: Sri Lanka</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Singapore. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Sri Lanka. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>アルファベット順どおり Singapore の位置。Commissioner か Alan Chow 氏か【TBC】。</t>
+          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Sri Lanka</t>
+          <t>Statement: the delegation of Thailand</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-19: Sri Lanka</t>
+          <t>PPT 09-19: Thailand</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Sri Lanka. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Thailand. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Thailand</t>
+          <t>Statement: the delegation of Turkiye</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-20: Thailand</t>
+          <t>PPT 09-20: Turkiye</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Thailand. You have 5 minutes, please.
+          <t>Next, I would like to invite the delegation of Turkiye. You have 5 minutes, please.
 （ステートメント 5分）
 Thank you very much.</t>
         </is>
@@ -2944,51 +2944,45 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Statement: the delegation of Turkiye</t>
+          <t>予備時間・Part 1 締め</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>PPT 09-21: Turkiye</t>
+          <t>PPT 11: Comments &amp; Questions（提出方法）</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the delegation of Turkiye. You have 5 minutes, please.
-（ステートメント 5分）
-Thank you very much.</t>
+          <t>We have a few minutes before the end of Part 1. If any delegation wishes to add a brief comment on what we have heard, please raise your name plate. [If none:] Please also use the comment sheets on your desk; they will be collected by the secretariat during the coffee break.</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>登録状況（9/16版リスト＋追加）で最終確認。未登録国は行を削除。</t>
+          <t>進行が押した場合はこの枠を吸収に使う。Azerbaijan（10/1）と Lao PDR（10/5）の発言辞退で 2 枠（10 分）空いた分もここに入る（14:43-14:55）。</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>着席発言（卓上マイク）</t>
+          <t>Moderator</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>紹介・御礼</t>
+          <t>進行</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>国名スライド</t>
+          <t>PPT 11</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>卓上マイク ON 確認</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: 発言者</t>
-        </is>
-      </c>
+          <t>スタンド/ハンドマイク</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="inlineStr">
         <is>
           <t>記録</t>
@@ -2999,174 +2993,105 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>発言者写真</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>Q&amp;A欄監視</t>
-        </is>
-      </c>
+      <c r="O38" s="7" t="n"/>
+      <c r="P38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>予備時間・Part 1 締め</t>
+          <t>RT Part 1 まとめ・連絡事項</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>PPT 11: Comments &amp; Questions（提出方法）</t>
+          <t>PPT 12: Info（Coffee / SC / Gala）</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>We have a few minutes before the end of Part 1. If any delegation wishes to add a brief comment on what we have heard, please raise your name plate. [If none:] Please also use the comment sheets on your desk; they will be collected by the secretariat during the coffee break.</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>進行が押した場合はこの枠を吸収に使う。Azerbaijan の発言辞退（10/1）で 1 枠（5 分）空いた分もここに入る（14:48-14:55）。</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Moderator</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>進行</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>PPT 11</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>スタンド/ハンドマイク</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>記録</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>記録</t>
-        </is>
-      </c>
-      <c r="O39" s="7" t="n"/>
-      <c r="P39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>RT Part 1 まとめ・連絡事項</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>PPT 12: Info（Coffee / SC / Gala）</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Thank you for your statements. This concludes Part 1 of the Roundtable. The remaining statements will be delivered tomorrow morning in Part 2, starting at 9 o’clock sharp in this room.
 Three announcements. First, coffee is served in front of this room. Second, the Steering Committee Meeting for ADRC member countries only will start at 15:15 in this room. Delegates of member countries, please return by 15:15. Third, for participants attending the SIDEX Gala Dinner, the bus will leave from Dorsett Changi City Hotel at 17:30. Thank you.</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>SC の前方席: 議長＝内閣府 中根補佐（内閣府スケジュール 9/28 版で「SC モデレーター」）、ADRC 宮木所長。SC 開始までに机上の RT 資料を回収（吉田・塩見）。</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Moderator</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>読み上げ</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>PPT 12</t>
         </is>
       </c>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Webinar 一時停止（SC は別 Zoom）</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>記録終了</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>記録終了</t>
         </is>
       </c>
-      <c r="O40" s="7" t="n"/>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="O39" s="7" t="n"/>
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>録画停止・保存</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="6" t="n">
+    <row r="40">
+      <c r="B40" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>15:00-15:15</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Coffee Break</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>コーヒー: Peridot 前。SC 用に前方席の名札を差し替え（吉田・田中）。Gerry は RT ノートを整理し Summary 執筆へ。</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
-      <c r="M41" s="6" t="n"/>
-      <c r="N41" s="6" t="n"/>
-      <c r="O41" s="6" t="n"/>
-      <c r="P41" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
